--- a/e2e-tests/Test Results/Excel/Automation_Test_Report.xlsx
+++ b/e2e-tests/Test Results/Excel/Automation_Test_Report.xlsx
@@ -504,7 +504,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Execution Date: 2026-08-19 09:47:43 | Build #: 001 | Pass Rate: 100.0%</t>
+          <t>Execution Date: 2026-08-19 10:06:17 | Build #: 001 | Pass Rate: 100.0%</t>
         </is>
       </c>
     </row>

--- a/e2e-tests/Test Results/Excel/Automation_Test_Report.xlsx
+++ b/e2e-tests/Test Results/Excel/Automation_Test_Report.xlsx
@@ -504,7 +504,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Execution Date: 2026-08-19 10:06:17 | Build #: 001 | Pass Rate: 100.0%</t>
+          <t>Execution Date: 2026-08-19 10:30:33 | Build #: 001 | Pass Rate: 100.0%</t>
         </is>
       </c>
     </row>

--- a/e2e-tests/Test Results/Excel/Automation_Test_Report.xlsx
+++ b/e2e-tests/Test Results/Excel/Automation_Test_Report.xlsx
@@ -504,7 +504,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Execution Date: 2026-08-19 10:30:33 | Build #: 001 | Pass Rate: 100.0%</t>
+          <t>Execution Date: 2026-08-19 11:19:59 | Build #: 001 | Pass Rate: 100.0%</t>
         </is>
       </c>
     </row>
